--- a/Datos y casos de prueba (1).xlsx
+++ b/Datos y casos de prueba (1).xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="36">
   <si>
     <t>ID</t>
   </si>
@@ -96,9 +96,6 @@
     <t xml:space="preserve">BPM </t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t xml:space="preserve"> #</t>
   </si>
   <si>
@@ -136,14 +133,28 @@
   </si>
   <si>
     <t>si</t>
+  </si>
+  <si>
+    <t>Mostrar lista ordenada por tempo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filtrar/Ordenar canciones por BPM </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -171,7 +182,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -194,11 +205,61 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="dashDotDot">
+        <color rgb="FF505050"/>
+      </left>
+      <right/>
+      <top style="dashDotDot">
+        <color rgb="FF505050"/>
+      </top>
+      <bottom style="dashDotDot">
+        <color rgb="FF505050"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="dashDotDot">
+        <color rgb="FF505050"/>
+      </top>
+      <bottom style="dashDotDot">
+        <color rgb="FF505050"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="dashDotDot">
+        <color rgb="FF505050"/>
+      </right>
+      <top style="dashDotDot">
+        <color rgb="FF505050"/>
+      </top>
+      <bottom style="dashDotDot">
+        <color rgb="FF505050"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashDotDot">
+        <color rgb="FF505050"/>
+      </left>
+      <right style="dashDotDot">
+        <color rgb="FF505050"/>
+      </right>
+      <top style="dashDotDot">
+        <color rgb="FF505050"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -212,6 +273,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -546,18 +621,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E7F4908-7696-684A-9573-236198F6E197}">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.125" customWidth="1"/>
     <col min="2" max="2" width="11.56640625" customWidth="1"/>
     <col min="3" max="4" width="11.1640625" customWidth="1"/>
     <col min="7" max="7" width="7.6640625" customWidth="1"/>
-    <col min="8" max="8" width="22.59765625" customWidth="1"/>
+    <col min="8" max="8" width="7.53125" customWidth="1"/>
     <col min="9" max="9" width="18.4296875" customWidth="1"/>
+    <col min="10" max="10" width="19.1015625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -573,20 +649,20 @@
       <c r="E1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="H1" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="I1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="J1" s="3" t="s">
-        <v>24</v>
-      </c>
     </row>
-    <row r="2" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -602,20 +678,20 @@
       <c r="E2" s="2">
         <v>105</v>
       </c>
-      <c r="G2" s="5">
+      <c r="H2" s="5">
         <v>1</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>25</v>
+      <c r="I2" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>34</v>
+        <v>24</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -631,20 +707,20 @@
       <c r="E3" s="2">
         <v>171</v>
       </c>
-      <c r="G3" s="5">
+      <c r="H3" s="5">
         <v>2</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>34</v>
+      <c r="I3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -660,20 +736,20 @@
       <c r="E4" s="2">
         <v>96</v>
       </c>
-      <c r="G4" s="5">
+      <c r="H4" s="5">
         <v>3</v>
       </c>
-      <c r="H4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>27</v>
+      <c r="I4" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>34</v>
+        <v>26</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="41.25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -689,20 +765,20 @@
       <c r="E5" s="2">
         <v>121</v>
       </c>
-      <c r="G5" s="5">
+      <c r="H5" s="11">
         <v>4</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="I5" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="K5" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="I5" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>34</v>
-      </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" ht="35.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -718,26 +794,35 @@
       <c r="E6" s="2">
         <v>91</v>
       </c>
+      <c r="H6" s="2">
+        <v>5</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>33</v>
+      </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A7" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="2">
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="10">
         <f>AVERAGE(E2:E6)</f>
         <v>116.8</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A7:D7"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>